--- a/data/labour-market/Trends in sustained destinations following 16–18 study in the GWE/Sustained destinations following 16-18 study GWE and England comparison.xlsx
+++ b/data/labour-market/Trends in sustained destinations following 16–18 study in the GWE/Sustained destinations following 16-18 study GWE and England comparison.xlsx
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
       <c r="AI2" s="2" t="inlineStr"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20657,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
       <c r="AI4" s="2" t="inlineStr"/>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
       <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20949,7 +20949,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
       <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21095,7 +21095,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21241,7 +21241,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
       <c r="AI8" s="2" t="inlineStr"/>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21387,7 +21387,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
       <c r="AI9" s="2" t="inlineStr"/>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21533,7 +21533,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
       <c r="AI10" s="2" t="inlineStr"/>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
       <c r="AI11" s="2" t="inlineStr"/>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
       <c r="AI12" s="2" t="inlineStr"/>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21971,7 +21971,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
       <c r="AI13" s="2" t="inlineStr"/>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22117,7 +22117,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
       <c r="AI14" s="2" t="inlineStr"/>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22263,7 +22263,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
       <c r="AI15" s="2" t="inlineStr"/>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
       <c r="AI16" s="2" t="inlineStr"/>
       <c r="AJ16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22555,7 +22555,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
       <c r="AI17" s="2" t="inlineStr"/>
       <c r="AJ17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22693,7 +22693,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
       <c r="AI18" s="2" t="inlineStr"/>
       <c r="AJ18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22839,7 +22839,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
       <c r="AI19" s="2" t="inlineStr"/>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22985,7 +22985,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
       <c r="AI20" s="2" t="inlineStr"/>
       <c r="AJ20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23131,7 +23131,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
       <c r="AI21" s="2" t="inlineStr"/>
       <c r="AJ21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23277,7 +23277,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
       <c r="AI22" s="2" t="inlineStr"/>
       <c r="AJ22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23423,7 +23423,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
       <c r="AI23" s="2" t="inlineStr"/>
       <c r="AJ23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23569,7 +23569,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
       <c r="AI24" s="2" t="inlineStr"/>
       <c r="AJ24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23715,7 +23715,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
       <c r="AI25" s="2" t="inlineStr"/>
       <c r="AJ25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23861,7 +23861,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
       <c r="AI26" s="2" t="inlineStr"/>
       <c r="AJ26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24007,7 +24007,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
       <c r="AI27" s="2" t="inlineStr"/>
       <c r="AJ27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24153,7 +24153,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
       <c r="AI28" s="2" t="inlineStr"/>
       <c r="AJ28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
       <c r="AI29" s="2" t="inlineStr"/>
       <c r="AJ29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24445,7 +24445,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
       <c r="AI30" s="2" t="inlineStr"/>
       <c r="AJ30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24591,7 +24591,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
       <c r="AI31" s="2" t="inlineStr"/>
       <c r="AJ31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24737,7 +24737,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
       <c r="AI32" s="2" t="inlineStr"/>
       <c r="AJ32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24875,7 +24875,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
       <c r="AI33" s="2" t="inlineStr"/>
       <c r="AJ33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25021,7 +25021,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
       <c r="AI34" s="2" t="inlineStr"/>
       <c r="AJ34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25167,7 +25167,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
       <c r="AI35" s="2" t="inlineStr"/>
       <c r="AJ35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25313,7 +25313,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
       <c r="AI36" s="2" t="inlineStr"/>
       <c r="AJ36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25459,7 +25459,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
       <c r="AI37" s="2" t="inlineStr"/>
       <c r="AJ37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25605,7 +25605,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
       <c r="AI38" s="2" t="inlineStr"/>
       <c r="AJ38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25751,7 +25751,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
       <c r="AI39" s="2" t="inlineStr"/>
       <c r="AJ39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25897,7 +25897,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
       <c r="AI40" s="2" t="inlineStr"/>
       <c r="AJ40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26043,7 +26043,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
       <c r="AI41" s="2" t="inlineStr"/>
       <c r="AJ41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
       <c r="AI42" s="2" t="inlineStr"/>
       <c r="AJ42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
       <c r="AI43" s="2" t="inlineStr"/>
       <c r="AJ43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
       <c r="AI44" s="2" t="inlineStr"/>
       <c r="AJ44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26627,7 +26627,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
       <c r="AI45" s="2" t="inlineStr"/>
       <c r="AJ45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26773,7 +26773,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
       <c r="AI46" s="2" t="inlineStr"/>
       <c r="AJ46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26919,7 +26919,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
       <c r="AI47" s="2" t="inlineStr"/>
       <c r="AJ47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27057,7 +27057,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
       <c r="AI48" s="2" t="inlineStr"/>
       <c r="AJ48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27203,7 +27203,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
       <c r="AI49" s="2" t="inlineStr"/>
       <c r="AJ49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27349,7 +27349,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
       <c r="AI50" s="2" t="inlineStr"/>
       <c r="AJ50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27495,7 +27495,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
       <c r="AI51" s="2" t="inlineStr"/>
       <c r="AJ51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27641,7 +27641,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
       <c r="AI52" s="2" t="inlineStr"/>
       <c r="AJ52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27787,7 +27787,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
       <c r="AI53" s="2" t="inlineStr"/>
       <c r="AJ53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27933,7 +27933,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
       <c r="AI54" s="2" t="inlineStr"/>
       <c r="AJ54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28079,7 +28079,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
       <c r="AI55" s="2" t="inlineStr"/>
       <c r="AJ55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28225,7 +28225,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
       <c r="AI56" s="2" t="inlineStr"/>
       <c r="AJ56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28371,7 +28371,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
       <c r="AI57" s="2" t="inlineStr"/>
       <c r="AJ57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28517,7 +28517,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -28627,7 +28627,7 @@
       <c r="AI58" s="2" t="inlineStr"/>
       <c r="AJ58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28663,7 +28663,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
       <c r="AI59" s="2" t="inlineStr"/>
       <c r="AJ59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28809,7 +28809,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
       <c r="AI60" s="2" t="inlineStr"/>
       <c r="AJ60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28955,7 +28955,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
       <c r="AI61" s="2" t="inlineStr"/>
       <c r="AJ61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -29101,7 +29101,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
       <c r="AI62" s="2" t="inlineStr"/>
       <c r="AJ62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
       <c r="AI63" s="2" t="inlineStr"/>
       <c r="AJ63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
       <c r="AI64" s="2" t="inlineStr"/>
       <c r="AJ64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -29531,7 +29531,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
       <c r="AI65" s="2" t="inlineStr"/>
       <c r="AJ65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -29677,7 +29677,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
       <c r="AI66" s="2" t="inlineStr"/>
       <c r="AJ66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -29823,7 +29823,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -29933,7 +29933,7 @@
       <c r="AI67" s="2" t="inlineStr"/>
       <c r="AJ67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -29969,7 +29969,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
       <c r="AI68" s="2" t="inlineStr"/>
       <c r="AJ68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -30115,7 +30115,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
       <c r="AI69" s="2" t="inlineStr"/>
       <c r="AJ69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -30261,7 +30261,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
       <c r="AI70" s="2" t="inlineStr"/>
       <c r="AJ70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -30407,7 +30407,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
       <c r="AI71" s="2" t="inlineStr"/>
       <c r="AJ71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -30553,7 +30553,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
       <c r="AI72" s="2" t="inlineStr"/>
       <c r="AJ72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -30699,7 +30699,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
       <c r="AI73" s="2" t="inlineStr"/>
       <c r="AJ73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -30845,7 +30845,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
       <c r="AI74" s="2" t="inlineStr"/>
       <c r="AJ74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -30991,7 +30991,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
       <c r="AI75" s="2" t="inlineStr"/>
       <c r="AJ75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -31137,7 +31137,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
       <c r="AI76" s="2" t="inlineStr"/>
       <c r="AJ76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -31283,7 +31283,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
       <c r="AI77" s="2" t="inlineStr"/>
       <c r="AJ77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -31421,7 +31421,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
       <c r="AI78" s="2" t="inlineStr"/>
       <c r="AJ78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -31567,7 +31567,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
       <c r="AI79" s="2" t="inlineStr"/>
       <c r="AJ79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -31713,7 +31713,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
       <c r="AI80" s="2" t="inlineStr"/>
       <c r="AJ80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -31859,7 +31859,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
       <c r="AI81" s="2" t="inlineStr"/>
       <c r="AJ81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -32005,7 +32005,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
       <c r="AI82" s="2" t="inlineStr"/>
       <c r="AJ82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -32151,7 +32151,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
       <c r="AI83" s="2" t="inlineStr"/>
       <c r="AJ83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -32297,7 +32297,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
       <c r="AI84" s="2" t="inlineStr"/>
       <c r="AJ84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -32443,7 +32443,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
       <c r="AI85" s="2" t="inlineStr"/>
       <c r="AJ85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -32589,7 +32589,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
       <c r="AI86" s="2" t="inlineStr"/>
       <c r="AJ86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -32735,7 +32735,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
       <c r="AI87" s="2" t="inlineStr"/>
       <c r="AJ87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -32881,7 +32881,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
       <c r="AI88" s="2" t="inlineStr"/>
       <c r="AJ88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -33027,7 +33027,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
       <c r="AI89" s="2" t="inlineStr"/>
       <c r="AJ89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -33173,7 +33173,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
       <c r="AI90" s="2" t="inlineStr"/>
       <c r="AJ90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -33319,7 +33319,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -33429,7 +33429,7 @@
       <c r="AI91" s="2" t="inlineStr"/>
       <c r="AJ91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -33465,7 +33465,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
       <c r="AI92" s="2" t="inlineStr"/>
       <c r="AJ92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -33603,7 +33603,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
       <c r="AI93" s="2" t="inlineStr"/>
       <c r="AJ93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -33749,7 +33749,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
       <c r="AI94" s="2" t="inlineStr"/>
       <c r="AJ94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -33895,7 +33895,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
       <c r="AI95" s="2" t="inlineStr"/>
       <c r="AJ95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -34041,7 +34041,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
       <c r="AI96" s="2" t="inlineStr"/>
       <c r="AJ96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -34187,7 +34187,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
       <c r="AI97" s="2" t="inlineStr"/>
       <c r="AJ97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -34333,7 +34333,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
       <c r="AI98" s="2" t="inlineStr"/>
       <c r="AJ98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -34479,7 +34479,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
       <c r="AI99" s="2" t="inlineStr"/>
       <c r="AJ99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -34625,7 +34625,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
       <c r="AI100" s="2" t="inlineStr"/>
       <c r="AJ100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -34771,7 +34771,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
       <c r="AI101" s="2" t="inlineStr"/>
       <c r="AJ101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -34917,7 +34917,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
       <c r="AI102" s="2" t="inlineStr"/>
       <c r="AJ102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -35063,7 +35063,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
       <c r="AI103" s="2" t="inlineStr"/>
       <c r="AJ103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -35209,7 +35209,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
       <c r="AI104" s="2" t="inlineStr"/>
       <c r="AJ104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -35355,7 +35355,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
       <c r="AI105" s="2" t="inlineStr"/>
       <c r="AJ105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -35501,7 +35501,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
       <c r="AI106" s="2" t="inlineStr"/>
       <c r="AJ106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -35647,7 +35647,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
       <c r="AI107" s="2" t="inlineStr"/>
       <c r="AJ107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -35785,7 +35785,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
       <c r="AI108" s="2" t="inlineStr"/>
       <c r="AJ108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -35931,7 +35931,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
       <c r="AI109" s="2" t="inlineStr"/>
       <c r="AJ109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -36077,7 +36077,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
       <c r="AI110" s="2" t="inlineStr"/>
       <c r="AJ110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -36223,7 +36223,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
       <c r="AI111" s="2" t="inlineStr"/>
       <c r="AJ111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -36369,7 +36369,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
       <c r="AI112" s="2" t="inlineStr"/>
       <c r="AJ112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -36515,7 +36515,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
       <c r="AI113" s="2" t="inlineStr"/>
       <c r="AJ113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -36661,7 +36661,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
       <c r="AI114" s="2" t="inlineStr"/>
       <c r="AJ114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
       <c r="AI115" s="2" t="inlineStr"/>
       <c r="AJ115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -36953,7 +36953,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
       <c r="AI116" s="2" t="inlineStr"/>
       <c r="AJ116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -37099,7 +37099,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
       <c r="AI117" s="2" t="inlineStr"/>
       <c r="AJ117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -37245,7 +37245,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
       <c r="AI118" s="2" t="inlineStr"/>
       <c r="AJ118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -37391,7 +37391,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
       <c r="AI119" s="2" t="inlineStr"/>
       <c r="AJ119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -37537,7 +37537,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
       <c r="AI120" s="2" t="inlineStr"/>
       <c r="AJ120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -37683,7 +37683,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
       <c r="AI121" s="2" t="inlineStr"/>
       <c r="AJ121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
       <c r="AI122" s="2" t="inlineStr"/>
       <c r="AJ122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -37967,7 +37967,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
       <c r="AI123" s="2" t="inlineStr"/>
       <c r="AJ123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -38113,7 +38113,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
       <c r="AI124" s="2" t="inlineStr"/>
       <c r="AJ124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -38259,7 +38259,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
       <c r="AI125" s="2" t="inlineStr"/>
       <c r="AJ125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -38405,7 +38405,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
       <c r="AI126" s="2" t="inlineStr"/>
       <c r="AJ126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -38551,7 +38551,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
       <c r="AI127" s="2" t="inlineStr"/>
       <c r="AJ127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -38697,7 +38697,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
       <c r="AI128" s="2" t="inlineStr"/>
       <c r="AJ128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -38843,7 +38843,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
       <c r="AI129" s="2" t="inlineStr"/>
       <c r="AJ129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -38989,7 +38989,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -39099,7 +39099,7 @@
       <c r="AI130" s="2" t="inlineStr"/>
       <c r="AJ130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -39135,7 +39135,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
       <c r="AI131" s="2" t="inlineStr"/>
       <c r="AJ131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -39281,7 +39281,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
       <c r="AI132" s="2" t="inlineStr"/>
       <c r="AJ132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -39427,7 +39427,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
       <c r="AI133" s="2" t="inlineStr"/>
       <c r="AJ133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -39573,7 +39573,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
       <c r="AI134" s="2" t="inlineStr"/>
       <c r="AJ134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -39719,7 +39719,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
       <c r="AI135" s="2" t="inlineStr"/>
       <c r="AJ135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -39865,7 +39865,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
       <c r="AI136" s="2" t="inlineStr"/>
       <c r="AJ136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -40011,7 +40011,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
       <c r="AI137" s="2" t="inlineStr"/>
       <c r="AJ137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -40149,7 +40149,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
       <c r="AI138" s="2" t="inlineStr"/>
       <c r="AJ138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -40295,7 +40295,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
       <c r="AI139" s="2" t="inlineStr"/>
       <c r="AJ139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -40441,7 +40441,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
       <c r="AI140" s="2" t="inlineStr"/>
       <c r="AJ140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -40587,7 +40587,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
       <c r="AI141" s="2" t="inlineStr"/>
       <c r="AJ141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -40733,7 +40733,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
       <c r="AI142" s="2" t="inlineStr"/>
       <c r="AJ142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -40879,7 +40879,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
       <c r="AI143" s="2" t="inlineStr"/>
       <c r="AJ143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -41025,7 +41025,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
       <c r="AI144" s="2" t="inlineStr"/>
       <c r="AJ144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -41171,7 +41171,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
       <c r="AI145" s="2" t="inlineStr"/>
       <c r="AJ145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -41317,7 +41317,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -41427,7 +41427,7 @@
       <c r="AI146" s="2" t="inlineStr"/>
       <c r="AJ146" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -41463,7 +41463,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
       <c r="AI147" s="2" t="inlineStr"/>
       <c r="AJ147" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -41609,7 +41609,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
       <c r="AI148" s="2" t="inlineStr"/>
       <c r="AJ148" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -41755,7 +41755,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
       <c r="AI149" s="2" t="inlineStr"/>
       <c r="AJ149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -41901,7 +41901,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
       <c r="AI150" s="2" t="inlineStr"/>
       <c r="AJ150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -42047,7 +42047,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
       <c r="AI151" s="2" t="inlineStr"/>
       <c r="AJ151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -42193,7 +42193,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
       <c r="AI152" s="2" t="inlineStr"/>
       <c r="AJ152" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -42331,7 +42331,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
       <c r="AI153" s="2" t="inlineStr"/>
       <c r="AJ153" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -42477,7 +42477,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
       <c r="AI154" s="2" t="inlineStr"/>
       <c r="AJ154" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -42623,7 +42623,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
       <c r="AI155" s="2" t="inlineStr"/>
       <c r="AJ155" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -42769,7 +42769,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
       <c r="AI156" s="2" t="inlineStr"/>
       <c r="AJ156" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -42915,7 +42915,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
       <c r="AI157" s="2" t="inlineStr"/>
       <c r="AJ157" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -43061,7 +43061,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
       <c r="AI158" s="2" t="inlineStr"/>
       <c r="AJ158" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -43207,7 +43207,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
       <c r="AI159" s="2" t="inlineStr"/>
       <c r="AJ159" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -43353,7 +43353,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
       <c r="AI160" s="2" t="inlineStr"/>
       <c r="AJ160" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -43499,7 +43499,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
       <c r="AI161" s="2" t="inlineStr"/>
       <c r="AJ161" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -43645,7 +43645,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
       <c r="AI162" s="2" t="inlineStr"/>
       <c r="AJ162" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -43791,7 +43791,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
       <c r="AI163" s="2" t="inlineStr"/>
       <c r="AJ163" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -43937,7 +43937,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
       <c r="AI164" s="2" t="inlineStr"/>
       <c r="AJ164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -44083,7 +44083,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
       <c r="AI165" s="2" t="inlineStr"/>
       <c r="AJ165" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -44229,7 +44229,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
       <c r="AI166" s="2" t="inlineStr"/>
       <c r="AJ166" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -44375,7 +44375,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
       <c r="AI167" s="2" t="inlineStr"/>
       <c r="AJ167" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
       <c r="AI168" s="2" t="inlineStr"/>
       <c r="AJ168" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -44659,7 +44659,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
       <c r="AI169" s="2" t="inlineStr"/>
       <c r="AJ169" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -44805,7 +44805,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
       <c r="AI170" s="2" t="inlineStr"/>
       <c r="AJ170" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -44951,7 +44951,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
       <c r="AI171" s="2" t="inlineStr"/>
       <c r="AJ171" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -45097,7 +45097,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
       <c r="AI172" s="2" t="inlineStr"/>
       <c r="AJ172" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -45243,7 +45243,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
       <c r="AI173" s="2" t="inlineStr"/>
       <c r="AJ173" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -45389,7 +45389,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
       <c r="AI174" s="2" t="inlineStr"/>
       <c r="AJ174" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -45535,7 +45535,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
       <c r="AI175" s="2" t="inlineStr"/>
       <c r="AJ175" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -45681,7 +45681,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
       <c r="AI176" s="2" t="inlineStr"/>
       <c r="AJ176" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -45827,7 +45827,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
       <c r="AI177" s="2" t="inlineStr"/>
       <c r="AJ177" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -45973,7 +45973,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
       <c r="AI178" s="2" t="inlineStr"/>
       <c r="AJ178" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -46119,7 +46119,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
       <c r="AI179" s="2" t="inlineStr"/>
       <c r="AJ179" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -46265,7 +46265,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
       <c r="AI180" s="2" t="inlineStr"/>
       <c r="AJ180" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -46411,7 +46411,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -46521,7 +46521,7 @@
       <c r="AI181" s="2" t="inlineStr"/>
       <c r="AJ181" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -46557,7 +46557,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -46659,7 +46659,7 @@
       <c r="AI182" s="2" t="inlineStr"/>
       <c r="AJ182" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -46695,7 +46695,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
       <c r="AI183" s="2" t="inlineStr"/>
       <c r="AJ183" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -46841,7 +46841,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
       <c r="AI184" s="2" t="inlineStr"/>
       <c r="AJ184" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -46987,7 +46987,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
       <c r="AI185" s="2" t="inlineStr"/>
       <c r="AJ185" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -47133,7 +47133,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
       <c r="AI186" s="2" t="inlineStr"/>
       <c r="AJ186" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -47279,7 +47279,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
       <c r="AI187" s="2" t="inlineStr"/>
       <c r="AJ187" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
       <c r="AI188" s="2" t="inlineStr"/>
       <c r="AJ188" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -47571,7 +47571,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
       <c r="AI189" s="2" t="inlineStr"/>
       <c r="AJ189" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -47717,7 +47717,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
       <c r="AI190" s="2" t="inlineStr"/>
       <c r="AJ190" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -47863,7 +47863,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
       <c r="AI191" s="2" t="inlineStr"/>
       <c r="AJ191" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -48009,7 +48009,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
       <c r="AI192" s="2" t="inlineStr"/>
       <c r="AJ192" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -48155,7 +48155,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
       <c r="AI193" s="2" t="inlineStr"/>
       <c r="AJ193" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -48301,7 +48301,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -48411,7 +48411,7 @@
       <c r="AI194" s="2" t="inlineStr"/>
       <c r="AJ194" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -48447,7 +48447,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
       <c r="AI195" s="2" t="inlineStr"/>
       <c r="AJ195" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -48593,7 +48593,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
       <c r="AI196" s="2" t="inlineStr"/>
       <c r="AJ196" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -48739,7 +48739,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
       <c r="AI197" s="2" t="inlineStr"/>
       <c r="AJ197" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -48877,7 +48877,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
       <c r="AI198" s="2" t="inlineStr"/>
       <c r="AJ198" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -49023,7 +49023,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
       <c r="AI199" s="2" t="inlineStr"/>
       <c r="AJ199" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -49169,7 +49169,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
       <c r="AI200" s="2" t="inlineStr"/>
       <c r="AJ200" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -49315,7 +49315,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
       <c r="AI201" s="2" t="inlineStr"/>
       <c r="AJ201" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -49461,7 +49461,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
       <c r="AI202" s="2" t="inlineStr"/>
       <c r="AJ202" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -49607,7 +49607,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
       <c r="AI203" s="2" t="inlineStr"/>
       <c r="AJ203" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -49753,7 +49753,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
       <c r="AI204" s="2" t="inlineStr"/>
       <c r="AJ204" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -49899,7 +49899,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
       <c r="AI205" s="2" t="inlineStr"/>
       <c r="AJ205" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -50045,7 +50045,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
       <c r="AI206" s="2" t="inlineStr"/>
       <c r="AJ206" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -50191,7 +50191,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -50301,7 +50301,7 @@
       <c r="AI207" s="2" t="inlineStr"/>
       <c r="AJ207" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
       <c r="AI208" s="2" t="inlineStr"/>
       <c r="AJ208" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -50483,7 +50483,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
       <c r="AI209" s="2" t="inlineStr"/>
       <c r="AJ209" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -50629,7 +50629,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
       <c r="AI210" s="2" t="inlineStr"/>
       <c r="AJ210" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -50775,7 +50775,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
       <c r="AI211" s="2" t="inlineStr"/>
       <c r="AJ211" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -50921,7 +50921,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
       <c r="AI212" s="2" t="inlineStr"/>
       <c r="AJ212" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -51059,7 +51059,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
       <c r="AI213" s="2" t="inlineStr"/>
       <c r="AJ213" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -51205,7 +51205,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
       <c r="AI214" s="2" t="inlineStr"/>
       <c r="AJ214" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -51351,7 +51351,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
       <c r="AI215" s="2" t="inlineStr"/>
       <c r="AJ215" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -51497,7 +51497,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
       <c r="AI216" s="2" t="inlineStr"/>
       <c r="AJ216" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -51643,7 +51643,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
       <c r="AI217" s="2" t="inlineStr"/>
       <c r="AJ217" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -51789,7 +51789,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
       <c r="AI218" s="2" t="inlineStr"/>
       <c r="AJ218" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -51935,7 +51935,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
       <c r="AI219" s="2" t="inlineStr"/>
       <c r="AJ219" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -52081,7 +52081,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
       <c r="AI220" s="2" t="inlineStr"/>
       <c r="AJ220" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -52227,7 +52227,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
       <c r="AI221" s="2" t="inlineStr"/>
       <c r="AJ221" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -52373,7 +52373,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
       <c r="AI222" s="2" t="inlineStr"/>
       <c r="AJ222" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -52519,7 +52519,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
       <c r="AI223" s="2" t="inlineStr"/>
       <c r="AJ223" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -52665,7 +52665,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
       <c r="AI224" s="2" t="inlineStr"/>
       <c r="AJ224" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -52811,7 +52811,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -52921,7 +52921,7 @@
       <c r="AI225" s="2" t="inlineStr"/>
       <c r="AJ225" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -52957,7 +52957,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -53067,7 +53067,7 @@
       <c r="AI226" s="2" t="inlineStr"/>
       <c r="AJ226" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -53103,7 +53103,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
       <c r="AI227" s="2" t="inlineStr"/>
       <c r="AJ227" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -53241,7 +53241,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
       <c r="AI228" s="2" t="inlineStr"/>
       <c r="AJ228" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -53387,7 +53387,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
       <c r="AI229" s="2" t="inlineStr"/>
       <c r="AJ229" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -53533,7 +53533,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
       <c r="AI230" s="2" t="inlineStr"/>
       <c r="AJ230" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -53679,7 +53679,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
       <c r="AI231" s="2" t="inlineStr"/>
       <c r="AJ231" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -53825,7 +53825,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
       <c r="AI232" s="2" t="inlineStr"/>
       <c r="AJ232" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -53971,7 +53971,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
       <c r="AI233" s="2" t="inlineStr"/>
       <c r="AJ233" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -54117,7 +54117,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
       <c r="AI234" s="2" t="inlineStr"/>
       <c r="AJ234" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -54263,7 +54263,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -54373,7 +54373,7 @@
       <c r="AI235" s="2" t="inlineStr"/>
       <c r="AJ235" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -54409,7 +54409,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
       <c r="AI236" s="2" t="inlineStr"/>
       <c r="AJ236" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -54555,7 +54555,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
       <c r="AI237" s="2" t="inlineStr"/>
       <c r="AJ237" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -54701,7 +54701,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -54811,7 +54811,7 @@
       <c r="AI238" s="2" t="inlineStr"/>
       <c r="AJ238" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -54847,7 +54847,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -54957,7 +54957,7 @@
       <c r="AI239" s="2" t="inlineStr"/>
       <c r="AJ239" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -54993,7 +54993,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -55103,7 +55103,7 @@
       <c r="AI240" s="2" t="inlineStr"/>
       <c r="AJ240" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -55139,7 +55139,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
       <c r="AI241" s="2" t="inlineStr"/>
       <c r="AJ241" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -55285,7 +55285,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -55387,7 +55387,7 @@
       <c r="AI242" s="2" t="inlineStr"/>
       <c r="AJ242" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -55423,7 +55423,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
       <c r="AI243" s="2" t="inlineStr"/>
       <c r="AJ243" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -55569,7 +55569,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -55679,7 +55679,7 @@
       <c r="AI244" s="2" t="inlineStr"/>
       <c r="AJ244" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -55715,7 +55715,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
       <c r="AI245" s="2" t="inlineStr"/>
       <c r="AJ245" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -55861,7 +55861,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
       <c r="AI246" s="2" t="inlineStr"/>
       <c r="AJ246" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -56007,7 +56007,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
       <c r="AI247" s="2" t="inlineStr"/>
       <c r="AJ247" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -56153,7 +56153,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -56263,7 +56263,7 @@
       <c r="AI248" s="2" t="inlineStr"/>
       <c r="AJ248" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -56299,7 +56299,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
       <c r="AI249" s="2" t="inlineStr"/>
       <c r="AJ249" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -56445,7 +56445,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
       <c r="AI250" s="2" t="inlineStr"/>
       <c r="AJ250" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -56701,7 +56701,7 @@
       <c r="AI251" s="2" t="inlineStr"/>
       <c r="AJ251" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -56737,7 +56737,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
       <c r="AI252" s="2" t="inlineStr"/>
       <c r="AJ252" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -56883,7 +56883,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -56993,7 +56993,7 @@
       <c r="AI253" s="2" t="inlineStr"/>
       <c r="AJ253" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -57029,7 +57029,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -57139,7 +57139,7 @@
       <c r="AI254" s="2" t="inlineStr"/>
       <c r="AJ254" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -57175,7 +57175,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -57285,7 +57285,7 @@
       <c r="AI255" s="2" t="inlineStr"/>
       <c r="AJ255" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -57321,7 +57321,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
       <c r="AI256" s="2" t="inlineStr"/>
       <c r="AJ256" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -57467,7 +57467,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -57569,7 +57569,7 @@
       <c r="AI257" s="2" t="inlineStr"/>
       <c r="AJ257" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -57605,7 +57605,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
       <c r="AI258" s="2" t="inlineStr"/>
       <c r="AJ258" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -57751,7 +57751,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -57861,7 +57861,7 @@
       <c r="AI259" s="2" t="inlineStr"/>
       <c r="AJ259" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -57897,7 +57897,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
       <c r="AI260" s="2" t="inlineStr"/>
       <c r="AJ260" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -58043,7 +58043,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
       <c r="AI261" s="2" t="inlineStr"/>
       <c r="AJ261" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -58189,7 +58189,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
       <c r="AI262" s="2" t="inlineStr"/>
       <c r="AJ262" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -58335,7 +58335,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
       <c r="AI263" s="2" t="inlineStr"/>
       <c r="AJ263" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -58481,7 +58481,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -58591,7 +58591,7 @@
       <c r="AI264" s="2" t="inlineStr"/>
       <c r="AJ264" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -58627,7 +58627,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
       <c r="AI265" s="2" t="inlineStr"/>
       <c r="AJ265" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -58773,7 +58773,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
       <c r="AI266" s="2" t="inlineStr"/>
       <c r="AJ266" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -58919,7 +58919,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -59029,7 +59029,7 @@
       <c r="AI267" s="2" t="inlineStr"/>
       <c r="AJ267" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -59065,7 +59065,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -59175,7 +59175,7 @@
       <c r="AI268" s="2" t="inlineStr"/>
       <c r="AJ268" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -59211,7 +59211,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
       <c r="AI269" s="2" t="inlineStr"/>
       <c r="AJ269" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -59357,7 +59357,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -59467,7 +59467,7 @@
       <c r="AI270" s="2" t="inlineStr"/>
       <c r="AJ270" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -59503,7 +59503,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -59613,7 +59613,7 @@
       <c r="AI271" s="2" t="inlineStr"/>
       <c r="AJ271" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       <c r="AI272" s="2" t="inlineStr"/>
       <c r="AJ272" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -59897,7 +59897,7 @@
       <c r="AI273" s="2" t="inlineStr"/>
       <c r="AJ273" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -60043,7 +60043,7 @@
       <c r="AI274" s="2" t="inlineStr"/>
       <c r="AJ274" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -60189,7 +60189,7 @@
       <c r="AI275" s="2" t="inlineStr"/>
       <c r="AJ275" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -60335,7 +60335,7 @@
       <c r="AI276" s="2" t="inlineStr"/>
       <c r="AJ276" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -60481,7 +60481,7 @@
       <c r="AI277" s="2" t="inlineStr"/>
       <c r="AJ277" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -60627,7 +60627,7 @@
       <c r="AI278" s="2" t="inlineStr"/>
       <c r="AJ278" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -60773,7 +60773,7 @@
       <c r="AI279" s="2" t="inlineStr"/>
       <c r="AJ279" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -60919,7 +60919,7 @@
       <c r="AI280" s="2" t="inlineStr"/>
       <c r="AJ280" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -61065,7 +61065,7 @@
       <c r="AI281" s="2" t="inlineStr"/>
       <c r="AJ281" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -61211,7 +61211,7 @@
       <c r="AI282" s="2" t="inlineStr"/>
       <c r="AJ282" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -61357,7 +61357,7 @@
       <c r="AI283" s="2" t="inlineStr"/>
       <c r="AJ283" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -61503,7 +61503,7 @@
       <c r="AI284" s="2" t="inlineStr"/>
       <c r="AJ284" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -61649,7 +61649,7 @@
       <c r="AI285" s="2" t="inlineStr"/>
       <c r="AJ285" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -61795,7 +61795,7 @@
       <c r="AI286" s="2" t="inlineStr"/>
       <c r="AJ286" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -61933,7 +61933,7 @@
       <c r="AI287" s="2" t="inlineStr"/>
       <c r="AJ287" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -62079,7 +62079,7 @@
       <c r="AI288" s="2" t="inlineStr"/>
       <c r="AJ288" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -62225,7 +62225,7 @@
       <c r="AI289" s="2" t="inlineStr"/>
       <c r="AJ289" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -62371,7 +62371,7 @@
       <c r="AI290" s="2" t="inlineStr"/>
       <c r="AJ290" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -62517,7 +62517,7 @@
       <c r="AI291" s="2" t="inlineStr"/>
       <c r="AJ291" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -62663,7 +62663,7 @@
       <c r="AI292" s="2" t="inlineStr"/>
       <c r="AJ292" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -62809,7 +62809,7 @@
       <c r="AI293" s="2" t="inlineStr"/>
       <c r="AJ293" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -62955,7 +62955,7 @@
       <c r="AI294" s="2" t="inlineStr"/>
       <c r="AJ294" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -63101,7 +63101,7 @@
       <c r="AI295" s="2" t="inlineStr"/>
       <c r="AJ295" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -63247,7 +63247,7 @@
       <c r="AI296" s="2" t="inlineStr"/>
       <c r="AJ296" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -63393,7 +63393,7 @@
       <c r="AI297" s="2" t="inlineStr"/>
       <c r="AJ297" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -63539,7 +63539,7 @@
       <c r="AI298" s="2" t="inlineStr"/>
       <c r="AJ298" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -63685,7 +63685,7 @@
       <c r="AI299" s="2" t="inlineStr"/>
       <c r="AJ299" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -63831,7 +63831,7 @@
       <c r="AI300" s="2" t="inlineStr"/>
       <c r="AJ300" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -63977,7 +63977,7 @@
       <c r="AI301" s="2" t="inlineStr"/>
       <c r="AJ301" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -64115,7 +64115,7 @@
       <c r="AI302" s="2" t="inlineStr"/>
       <c r="AJ302" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -64261,7 +64261,7 @@
       <c r="AI303" s="2" t="inlineStr"/>
       <c r="AJ303" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -64407,7 +64407,7 @@
       <c r="AI304" s="2" t="inlineStr"/>
       <c r="AJ304" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -64553,7 +64553,7 @@
       <c r="AI305" s="2" t="inlineStr"/>
       <c r="AJ305" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -64699,7 +64699,7 @@
       <c r="AI306" s="2" t="inlineStr"/>
       <c r="AJ306" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -64845,7 +64845,7 @@
       <c r="AI307" s="2" t="inlineStr"/>
       <c r="AJ307" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -64991,7 +64991,7 @@
       <c r="AI308" s="2" t="inlineStr"/>
       <c r="AJ308" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -65137,7 +65137,7 @@
       <c r="AI309" s="2" t="inlineStr"/>
       <c r="AJ309" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -65283,7 +65283,7 @@
       <c r="AI310" s="2" t="inlineStr"/>
       <c r="AJ310" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -65429,7 +65429,7 @@
       <c r="AI311" s="2" t="inlineStr"/>
       <c r="AJ311" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -65575,7 +65575,7 @@
       <c r="AI312" s="2" t="inlineStr"/>
       <c r="AJ312" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -65721,7 +65721,7 @@
       <c r="AI313" s="2" t="inlineStr"/>
       <c r="AJ313" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -65867,7 +65867,7 @@
       <c r="AI314" s="2" t="inlineStr"/>
       <c r="AJ314" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -66013,7 +66013,7 @@
       <c r="AI315" s="2" t="inlineStr"/>
       <c r="AJ315" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -66159,7 +66159,7 @@
       <c r="AI316" s="2" t="inlineStr"/>
       <c r="AJ316" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -66285,7 +66285,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>21 July 2026</t>
+          <t>22 July 2026</t>
         </is>
       </c>
     </row>
